--- a/public/modeles/modele-facture-acompte.xlsx
+++ b/public/modeles/modele-facture-acompte.xlsx
@@ -32,8 +32,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="60" formatCode="#  ##0.00"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -526,14 +527,14 @@
       <c r="A24" t="str">
         <v>Acompte de [30 %] sur [libellé du devis]</v>
       </c>
-      <c r="B24" t="str">
-        <v>5 000,00</v>
+      <c r="B24">
+        <v>5000</v>
       </c>
       <c r="C24" t="str">
         <v>20 %</v>
       </c>
-      <c r="D24" t="str">
-        <v>1 500,00</v>
+      <c r="D24">
+        <v>1500</v>
       </c>
     </row>
     <row r="25">
@@ -581,12 +582,12 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Cette facture d'acompte se rapporte au devis [D-2026-001] d'un montant total de [5 000,00 € HT].</v>
+        <v>Cette facture d'acompte se rapporte au devis [D-2026-001] d'un montant total de [5 000,00 euros HT].</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>La facture de solde déduira l'acompte : Total HT 5 000,00 € - acompte 1 500,00 € = 3 500,00 € HT à facturer.</v>
+        <v>La facture de solde déduira l'acompte : Total HT 5 000,00 euros - acompte 1 500,00 euros = 3 500,00 euros HT à facturer.</v>
       </c>
     </row>
     <row r="34">
@@ -596,7 +597,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>En cas de retard, pénalités au taux de [3 fois le taux d'intérêt légal] et indemnité forfaitaire de 40 €.</v>
+        <v>En cas de retard, pénalités au taux de [3 fois le taux d'intérêt légal] et indemnité forfaitaire de 40 euros.</v>
       </c>
     </row>
     <row r="37">
